--- a/docentes/Hernández Contreras Ángel - Estadisticos 20222.xlsx
+++ b/docentes/Hernández Contreras Ángel - Estadisticos 20222.xlsx
@@ -562,16 +562,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>88.23999999999999</v>
+      </c>
+      <c r="H2">
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -585,16 +588,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>96.43000000000001</v>
+      </c>
+      <c r="H3">
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -650,16 +656,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>94.12</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -685,7 +691,7 @@
         <v>96.43000000000001</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Hernández Contreras Ángel - Estadisticos 20222.xlsx
+++ b/docentes/Hernández Contreras Ángel - Estadisticos 20222.xlsx
@@ -656,16 +656,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -682,16 +682,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>96.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
